--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G4_task074.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G4_task074.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -691,6 +691,94 @@
         <v>4.257883340972902</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>359</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1108</v>
+      </c>
+      <c r="C14" s="0">
+        <v>359</v>
+      </c>
+      <c r="D14" s="0">
+        <v>93.393449106943365</v>
+      </c>
+      <c r="E14" s="0">
+        <v>491.77000000000004</v>
+      </c>
+      <c r="F14" s="0">
+        <v>149.76837174601309</v>
+      </c>
+      <c r="G14" s="0">
+        <v>6412.9532691950981</v>
+      </c>
+      <c r="H14" s="0">
+        <v>-1372.52244758395</v>
+      </c>
+      <c r="I14" s="0">
+        <v>7.0300000000000002</v>
+      </c>
+      <c r="J14" s="0">
+        <v>19.66</v>
+      </c>
+      <c r="K14" s="0">
+        <v>3.1400000000000006</v>
+      </c>
+      <c r="L14" s="0">
+        <v>4.6100000000000012</v>
+      </c>
+      <c r="M14" s="0">
+        <v>240.98193352487564</v>
+      </c>
+      <c r="N14" s="0">
+        <v>4.257883340972902</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>359</v>
+      </c>
+      <c r="B15" s="0">
+        <v>1109</v>
+      </c>
+      <c r="C15" s="0">
+        <v>359</v>
+      </c>
+      <c r="D15" s="0">
+        <v>93.385604716355601</v>
+      </c>
+      <c r="E15" s="0">
+        <v>492.92000000000002</v>
+      </c>
+      <c r="F15" s="0">
+        <v>149.41895677500784</v>
+      </c>
+      <c r="G15" s="0">
+        <v>6434.4567898959513</v>
+      </c>
+      <c r="H15" s="0">
+        <v>-1369.3597996488977</v>
+      </c>
+      <c r="I15" s="0">
+        <v>7.0499999999999998</v>
+      </c>
+      <c r="J15" s="0">
+        <v>19.905000000000001</v>
+      </c>
+      <c r="K15" s="0">
+        <v>3.1699999999999999</v>
+      </c>
+      <c r="L15" s="0">
+        <v>4.6449999999999996</v>
+      </c>
+      <c r="M15" s="0">
+        <v>240.97551490686925</v>
+      </c>
+      <c r="N15" s="0">
+        <v>4.2586643561945134</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G4_task074.xlsx
+++ b/Data_Analysis/Sensitivity analysis/Hybrid/sweep_results_hybrid_G4_task074.xlsx
@@ -100,7 +100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="true"/>
@@ -779,6 +779,50 @@
         <v>4.2586643561945134</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>359</v>
+      </c>
+      <c r="B16" s="0">
+        <v>1110</v>
+      </c>
+      <c r="C16" s="0">
+        <v>359</v>
+      </c>
+      <c r="D16" s="0">
+        <v>93.385604716355601</v>
+      </c>
+      <c r="E16" s="0">
+        <v>492.92000000000002</v>
+      </c>
+      <c r="F16" s="0">
+        <v>149.41895677500784</v>
+      </c>
+      <c r="G16" s="0">
+        <v>6434.4567898959513</v>
+      </c>
+      <c r="H16" s="0">
+        <v>-1369.3597996488977</v>
+      </c>
+      <c r="I16" s="0">
+        <v>7.0499999999999998</v>
+      </c>
+      <c r="J16" s="0">
+        <v>19.905000000000001</v>
+      </c>
+      <c r="K16" s="0">
+        <v>3.1699999999999999</v>
+      </c>
+      <c r="L16" s="0">
+        <v>4.6449999999999996</v>
+      </c>
+      <c r="M16" s="0">
+        <v>240.97551490686925</v>
+      </c>
+      <c r="N16" s="0">
+        <v>4.2586643561945134</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>